--- a/salidas/empresas/CSCO.xlsx
+++ b/salidas/empresas/CSCO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>11.90644645690918</v>
+        <v>11.9064416885376</v>
       </c>
       <c r="C2" t="n">
         <v>18.56999969482422</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>13.89405822753906</v>
+        <v>13.89405632019043</v>
       </c>
       <c r="C4" t="n">
         <v>21.67000007629395</v>
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>12.61813831329346</v>
+        <v>12.61813640594482</v>
       </c>
       <c r="C6" t="n">
         <v>19.68000030517578</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>12.5219612121582</v>
+        <v>12.52196502685547</v>
       </c>
       <c r="C7" t="n">
         <v>19.53000068664551</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>11.46404075622559</v>
+        <v>11.46403884887695</v>
       </c>
       <c r="C8" t="n">
         <v>17.8799991607666</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>14.09922695159912</v>
+        <v>14.09923076629639</v>
       </c>
       <c r="C9" t="n">
         <v>21.98999977111816</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.73398494720459</v>
+        <v>14.73398208618164</v>
       </c>
       <c r="C10" t="n">
         <v>22.97999954223633</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>15.47132110595703</v>
+        <v>15.4713249206543</v>
       </c>
       <c r="C11" t="n">
         <v>24.1299991607666</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>17.25375556945801</v>
+        <v>17.25376129150391</v>
       </c>
       <c r="C12" t="n">
         <v>26.90999984741211</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>17.52305603027344</v>
+        <v>17.5230541229248</v>
       </c>
       <c r="C13" t="n">
         <v>27.32999992370605</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>17.06782531738281</v>
+        <v>17.06782722473145</v>
       </c>
       <c r="C14" t="n">
         <v>26.6200008392334</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>16.6318302154541</v>
+        <v>16.63183403015137</v>
       </c>
       <c r="C15" t="n">
         <v>25.94000053405762</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>16.36895370483398</v>
+        <v>16.36895751953125</v>
       </c>
       <c r="C16" t="n">
         <v>25.53000068664551</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>17.14477157592773</v>
+        <v>17.14477729797363</v>
       </c>
       <c r="C17" t="n">
         <v>26.73999977111816</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>17.26017189025879</v>
+        <v>17.26017379760742</v>
       </c>
       <c r="C18" t="n">
         <v>26.92000007629395</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>17.8564567565918</v>
+        <v>17.85645484924316</v>
       </c>
       <c r="C19" t="n">
         <v>27.85000038146973</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>18.53609466552734</v>
+        <v>18.53610038757324</v>
       </c>
       <c r="C20" t="n">
         <v>28.90999984741211</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>20.46601295471191</v>
+        <v>20.46600151062012</v>
       </c>
       <c r="C21" t="n">
         <v>31.92000007629395</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>21.2418098449707</v>
+        <v>21.2418155670166</v>
       </c>
       <c r="C22" t="n">
         <v>33.13000106811523</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>21.19692802429199</v>
+        <v>21.19692993164062</v>
       </c>
       <c r="C23" t="n">
         <v>33.06000137329102</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>17.9654598236084</v>
+        <v>17.96545600891113</v>
       </c>
       <c r="C24" t="n">
         <v>28.02000045776367</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>17.35635375976562</v>
+        <v>17.35635185241699</v>
       </c>
       <c r="C25" t="n">
         <v>27.06999969482422</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>15.70855617523193</v>
+        <v>15.70855522155762</v>
       </c>
       <c r="C26" t="n">
         <v>24.5</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>15.63803195953369</v>
+        <v>15.63802242279053</v>
       </c>
       <c r="C27" t="n">
         <v>24.38999938964844</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>16.43949127197266</v>
+        <v>16.43949317932129</v>
       </c>
       <c r="C29" t="n">
         <v>25.63999938964844</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>17.13194274902344</v>
+        <v>17.1319408416748</v>
       </c>
       <c r="C30" t="n">
         <v>26.71999931335449</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>14.91351127624512</v>
+        <v>14.91351318359375</v>
       </c>
       <c r="C31" t="n">
         <v>23.26000022888184</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>14.09922695159912</v>
+        <v>14.09923076629639</v>
       </c>
       <c r="C32" t="n">
         <v>21.98999977111816</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>15.42002582550049</v>
+        <v>15.42002964019775</v>
       </c>
       <c r="C33" t="n">
         <v>24.04999923706055</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>14.46469020843506</v>
+        <v>14.46469688415527</v>
       </c>
       <c r="C34" t="n">
         <v>22.55999946594238</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>11.39351081848145</v>
+        <v>11.39351177215576</v>
       </c>
       <c r="C35" t="n">
         <v>17.77000045776367</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>10.60488033294678</v>
+        <v>10.60487842559814</v>
       </c>
       <c r="C36" t="n">
         <v>16.54000091552734</v>
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>9.598249435424805</v>
+        <v>9.598246574401855</v>
       </c>
       <c r="C38" t="n">
         <v>14.97000026702881</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>9.341780662536621</v>
+        <v>9.341781616210938</v>
       </c>
       <c r="C39" t="n">
         <v>14.56999969482422</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>10.75234603881836</v>
+        <v>10.75235271453857</v>
       </c>
       <c r="C40" t="n">
         <v>16.77000045776367</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>12.38732147216797</v>
+        <v>12.38731861114502</v>
       </c>
       <c r="C41" t="n">
         <v>19.31999969482422</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>11.86156272888184</v>
+        <v>11.8615608215332</v>
       </c>
       <c r="C42" t="n">
         <v>18.5</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>14.11205005645752</v>
+        <v>14.11205577850342</v>
       </c>
       <c r="C44" t="n">
         <v>22.01000022888184</v>
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>15.09303951263428</v>
+        <v>15.09304046630859</v>
       </c>
       <c r="C46" t="n">
         <v>23.54000091552734</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>14.6249885559082</v>
+        <v>14.62498092651367</v>
       </c>
       <c r="C47" t="n">
         <v>22.80999946594238</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>15.00327777862549</v>
+        <v>15.00326919555664</v>
       </c>
       <c r="C48" t="n">
         <v>23.39999961853027</v>
@@ -1381,11 +1393,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>15.34950828552246</v>
+        <v>15.34950351715088</v>
       </c>
       <c r="C49" t="n">
         <v>23.94000053405762</v>
@@ -1406,11 +1418,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>14.4069881439209</v>
+        <v>14.40698623657227</v>
       </c>
       <c r="C50" t="n">
         <v>22.46999931335449</v>
@@ -1431,11 +1443,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>15.59956645965576</v>
+        <v>15.59955883026123</v>
       </c>
       <c r="C51" t="n">
         <v>24.32999992370605</v>
@@ -1456,7 +1468,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1481,11 +1493,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>17.2665958404541</v>
+        <v>17.26658821105957</v>
       </c>
       <c r="C53" t="n">
         <v>26.93000030517578</v>
@@ -1506,11 +1518,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>14.84939670562744</v>
+        <v>14.84939098358154</v>
       </c>
       <c r="C54" t="n">
         <v>23.15999984741211</v>
@@ -1531,11 +1543,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>13.66323757171631</v>
+        <v>13.66323661804199</v>
       </c>
       <c r="C55" t="n">
         <v>21.30999946594238</v>
@@ -1556,11 +1568,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>14.79168796539307</v>
+        <v>14.79169368743896</v>
       </c>
       <c r="C56" t="n">
         <v>23.06999969482422</v>
@@ -1581,11 +1593,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>12.81689834594727</v>
+        <v>12.81689739227295</v>
       </c>
       <c r="C57" t="n">
         <v>19.98999977111816</v>
@@ -1606,11 +1618,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>14.04152679443359</v>
+        <v>14.04152488708496</v>
       </c>
       <c r="C58" t="n">
         <v>21.89999961853027</v>
@@ -1635,11 +1647,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>14.65704250335693</v>
+        <v>14.65704536437988</v>
       </c>
       <c r="C59" t="n">
         <v>22.86000061035156</v>
@@ -1664,11 +1676,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>12.28472900390625</v>
+        <v>12.28473377227783</v>
       </c>
       <c r="C60" t="n">
         <v>19.15999984741211</v>
@@ -1693,11 +1705,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>12.97078323364258</v>
+        <v>12.97077941894531</v>
       </c>
       <c r="C61" t="n">
         <v>20.22999954223633</v>
@@ -1722,11 +1734,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>13.56064987182617</v>
+        <v>13.56065082550049</v>
       </c>
       <c r="C62" t="n">
         <v>21.14999961853027</v>
@@ -1751,11 +1763,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>11.90003108978271</v>
+        <v>11.90003204345703</v>
       </c>
       <c r="C63" t="n">
         <v>18.55999946594238</v>
@@ -1780,11 +1792,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>11.03450012207031</v>
+        <v>11.03450298309326</v>
       </c>
       <c r="C64" t="n">
         <v>17.14999961853027</v>
@@ -1809,11 +1821,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>11.2725658416748</v>
+        <v>11.27256298065186</v>
       </c>
       <c r="C65" t="n">
         <v>17.52000045776367</v>
@@ -1838,11 +1850,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.80930805206299</v>
+        <v>10.80930709838867</v>
       </c>
       <c r="C66" t="n">
         <v>16.79999923706055</v>
@@ -1867,7 +1879,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1896,11 +1908,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>10.31429672241211</v>
+        <v>10.31429576873779</v>
       </c>
       <c r="C68" t="n">
         <v>15.97000026702881</v>
@@ -1925,11 +1937,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>10.12054252624512</v>
+        <v>10.12053966522217</v>
       </c>
       <c r="C69" t="n">
         <v>15.67000007629395</v>
@@ -1954,11 +1966,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>10.01074600219727</v>
+        <v>10.01074695587158</v>
       </c>
       <c r="C70" t="n">
         <v>15.5</v>
@@ -1983,11 +1995,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>12.01514720916748</v>
+        <v>12.01514434814453</v>
       </c>
       <c r="C71" t="n">
         <v>18.53000068664551</v>
@@ -2012,11 +2024,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>12.08646965026855</v>
+        <v>12.08647155761719</v>
       </c>
       <c r="C72" t="n">
         <v>18.63999938964844</v>
@@ -2041,11 +2053,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>11.72336006164551</v>
+        <v>11.72335720062256</v>
       </c>
       <c r="C73" t="n">
         <v>18.07999992370605</v>
@@ -2070,11 +2082,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>12.78379058837891</v>
+        <v>12.7837963104248</v>
       </c>
       <c r="C74" t="n">
         <v>19.64999961853027</v>
@@ -2099,11 +2111,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>12.93342208862305</v>
+        <v>12.93342781066895</v>
       </c>
       <c r="C75" t="n">
         <v>19.8799991607666</v>
@@ -2128,7 +2140,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2157,11 +2169,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>13.1652946472168</v>
+        <v>13.16529560089111</v>
       </c>
       <c r="C77" t="n">
         <v>20.15999984741211</v>
@@ -2186,11 +2198,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>10.66414546966553</v>
+        <v>10.66414928436279</v>
       </c>
       <c r="C78" t="n">
         <v>16.32999992370605</v>
@@ -2215,11 +2227,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>11.21269989013672</v>
+        <v>11.2127046585083</v>
       </c>
       <c r="C79" t="n">
         <v>17.17000007629395</v>
@@ -2244,11 +2256,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>10.46474933624268</v>
+        <v>10.46475315093994</v>
       </c>
       <c r="C80" t="n">
         <v>15.94999980926514</v>
@@ -2273,11 +2285,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>12.51833343505859</v>
+        <v>12.51833534240723</v>
       </c>
       <c r="C81" t="n">
         <v>19.07999992370605</v>
@@ -2302,11 +2314,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>12.53145694732666</v>
+        <v>12.53145313262939</v>
       </c>
       <c r="C82" t="n">
         <v>19.10000038146973</v>
@@ -2331,11 +2343,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>11.33541393280029</v>
+        <v>11.33541870117188</v>
       </c>
       <c r="C83" t="n">
         <v>17.14999961853027</v>
@@ -2360,11 +2372,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>12.59118938446045</v>
+        <v>12.59118461608887</v>
       </c>
       <c r="C84" t="n">
         <v>18.90999984741211</v>
@@ -2389,11 +2401,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>13.08391094207764</v>
+        <v>13.0839147567749</v>
       </c>
       <c r="C85" t="n">
         <v>19.64999961853027</v>
@@ -2418,11 +2430,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>13.69649028778076</v>
+        <v>13.69649600982666</v>
       </c>
       <c r="C86" t="n">
         <v>20.56999969482422</v>
@@ -2447,11 +2459,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>13.88959217071533</v>
+        <v>13.88958930969238</v>
       </c>
       <c r="C87" t="n">
         <v>20.86000061035156</v>
@@ -2476,11 +2488,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>13.91622352600098</v>
+        <v>13.91622924804688</v>
       </c>
       <c r="C88" t="n">
         <v>20.89999961853027</v>
@@ -2505,11 +2517,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>14.04213714599609</v>
+        <v>14.04214668273926</v>
       </c>
       <c r="C89" t="n">
         <v>20.92000007629395</v>
@@ -2534,11 +2546,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>16.19008255004883</v>
+        <v>16.19007873535156</v>
       </c>
       <c r="C90" t="n">
         <v>24.1200008392334</v>
@@ -2563,11 +2575,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>16.3377513885498</v>
+        <v>16.33775520324707</v>
       </c>
       <c r="C91" t="n">
         <v>24.34000015258789</v>
@@ -2592,11 +2604,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>17.29760360717773</v>
+        <v>17.297607421875</v>
       </c>
       <c r="C92" t="n">
         <v>25.59000015258789</v>
@@ -2621,11 +2633,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>15.75643157958984</v>
+        <v>15.75642871856689</v>
       </c>
       <c r="C93" t="n">
         <v>23.30999946594238</v>
@@ -2650,11 +2662,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>15.83754062652588</v>
+        <v>15.83754634857178</v>
       </c>
       <c r="C94" t="n">
         <v>23.43000030517578</v>
@@ -2679,11 +2691,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>15.36091899871826</v>
+        <v>15.36092185974121</v>
       </c>
       <c r="C95" t="n">
         <v>22.55999946594238</v>
@@ -2708,11 +2720,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>14.46895408630371</v>
+        <v>14.46895503997803</v>
       </c>
       <c r="C96" t="n">
         <v>21.25</v>
@@ -2737,11 +2749,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>15.27240180969238</v>
+        <v>15.27240562438965</v>
       </c>
       <c r="C97" t="n">
         <v>22.43000030517578</v>
@@ -2766,11 +2778,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>15.03227519989014</v>
+        <v>15.03227615356445</v>
       </c>
       <c r="C98" t="n">
         <v>21.90999984741211</v>
@@ -2795,11 +2807,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>14.95680809020996</v>
+        <v>14.95680332183838</v>
       </c>
       <c r="C99" t="n">
         <v>21.79999923706055</v>
@@ -2824,11 +2836,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>15.38218307495117</v>
+        <v>15.38217926025391</v>
       </c>
       <c r="C100" t="n">
         <v>22.42000007629395</v>
@@ -2853,11 +2865,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>15.99110698699951</v>
+        <v>15.99109935760498</v>
       </c>
       <c r="C101" t="n">
         <v>23.11000061035156</v>
@@ -2882,11 +2894,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>17.03595352172852</v>
+        <v>17.03595733642578</v>
       </c>
       <c r="C102" t="n">
         <v>24.6200008392334</v>
@@ -2911,11 +2923,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>17.19510841369629</v>
+        <v>17.19510459899902</v>
       </c>
       <c r="C103" t="n">
         <v>24.85000038146973</v>
@@ -2940,11 +2952,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>17.59131622314453</v>
+        <v>17.5913143157959</v>
       </c>
       <c r="C104" t="n">
         <v>25.22999954223633</v>
@@ -2969,11 +2981,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>17.42398452758789</v>
+        <v>17.42398071289062</v>
       </c>
       <c r="C105" t="n">
         <v>24.98999977111816</v>
@@ -2998,11 +3010,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>17.6832332611084</v>
+        <v>17.68324089050293</v>
       </c>
       <c r="C106" t="n">
         <v>25.17000007629395</v>
@@ -3027,11 +3039,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>17.19144821166992</v>
+        <v>17.19144630432129</v>
       </c>
       <c r="C107" t="n">
         <v>24.46999931335449</v>
@@ -3056,11 +3068,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>19.41853713989258</v>
+        <v>19.41854095458984</v>
       </c>
       <c r="C108" t="n">
         <v>27.63999938964844</v>
@@ -3085,11 +3097,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>19.54499816894531</v>
+        <v>19.54499626159668</v>
       </c>
       <c r="C109" t="n">
         <v>27.81999969482422</v>
@@ -3114,11 +3126,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>18.65369415283203</v>
+        <v>18.65369606018066</v>
       </c>
       <c r="C110" t="n">
         <v>26.3700008392334</v>
@@ -3143,11 +3155,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>20.87487602233887</v>
+        <v>20.8748722076416</v>
       </c>
       <c r="C111" t="n">
         <v>29.51000022888184</v>
@@ -3172,11 +3184,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>19.62329483032227</v>
+        <v>19.6232967376709</v>
       </c>
       <c r="C112" t="n">
         <v>27.53000068664551</v>
@@ -3201,11 +3213,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>20.54993438720703</v>
+        <v>20.54992866516113</v>
       </c>
       <c r="C113" t="n">
         <v>28.82999992370605</v>
@@ -3230,11 +3242,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>20.8920726776123</v>
+        <v>20.8920783996582</v>
       </c>
       <c r="C114" t="n">
         <v>29.30999946594238</v>
@@ -3259,11 +3271,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>19.57339668273926</v>
+        <v>19.57340049743652</v>
       </c>
       <c r="C115" t="n">
         <v>27.45999908447266</v>
@@ -3288,11 +3300,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>20.41380500793457</v>
+        <v>20.41379928588867</v>
       </c>
       <c r="C116" t="n">
         <v>28.42000007629395</v>
@@ -3317,11 +3329,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>18.58934593200684</v>
+        <v>18.58934020996094</v>
       </c>
       <c r="C117" t="n">
         <v>25.8799991607666</v>
@@ -3346,11 +3358,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>18.85511207580566</v>
+        <v>18.8551139831543</v>
       </c>
       <c r="C118" t="n">
         <v>26.25</v>
@@ -3375,11 +3387,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>20.88978576660156</v>
+        <v>20.8897819519043</v>
       </c>
       <c r="C119" t="n">
         <v>28.85000038146973</v>
@@ -3404,11 +3416,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>19.73124504089355</v>
+        <v>19.73125076293945</v>
       </c>
       <c r="C120" t="n">
         <v>27.25</v>
@@ -3433,11 +3445,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>19.66609001159668</v>
+        <v>19.66608238220215</v>
       </c>
       <c r="C121" t="n">
         <v>27.15999984741211</v>
@@ -3462,11 +3474,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>17.36015510559082</v>
+        <v>17.36015319824219</v>
       </c>
       <c r="C122" t="n">
         <v>23.79000091552734</v>
@@ -3491,11 +3503,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>19.10419654846191</v>
+        <v>19.10420036315918</v>
       </c>
       <c r="C123" t="n">
         <v>26.18000030517578</v>
@@ -3520,11 +3532,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>20.77526092529297</v>
+        <v>20.7752685546875</v>
       </c>
       <c r="C124" t="n">
         <v>28.46999931335449</v>
@@ -3549,11 +3561,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>20.24359321594238</v>
+        <v>20.24358749389648</v>
       </c>
       <c r="C125" t="n">
         <v>27.48999977111816</v>
@@ -3578,11 +3590,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>21.39237403869629</v>
+        <v>21.39237594604492</v>
       </c>
       <c r="C126" t="n">
         <v>29.04999923706055</v>
@@ -3607,11 +3619,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>21.12726783752441</v>
+        <v>21.12726211547852</v>
       </c>
       <c r="C127" t="n">
         <v>28.69000053405762</v>
@@ -3636,7 +3648,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3665,11 +3677,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>23.3632869720459</v>
+        <v>23.36328315734863</v>
       </c>
       <c r="C129" t="n">
         <v>31.44000053405762</v>
@@ -3694,11 +3706,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>23.57135581970215</v>
+        <v>23.57135200500488</v>
       </c>
       <c r="C130" t="n">
         <v>31.71999931335449</v>
@@ -3723,11 +3735,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>22.9869384765625</v>
+        <v>22.98693656921387</v>
       </c>
       <c r="C131" t="n">
         <v>30.68000030517578</v>
@@ -3752,11 +3764,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>22.34258842468262</v>
+        <v>22.34259223937988</v>
       </c>
       <c r="C132" t="n">
         <v>29.81999969482422</v>
@@ -3781,11 +3793,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>22.64229011535645</v>
+        <v>22.64228057861328</v>
       </c>
       <c r="C133" t="n">
         <v>30.21999931335449</v>
@@ -3810,11 +3822,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>23.21454620361328</v>
+        <v>23.21454238891602</v>
       </c>
       <c r="C134" t="n">
         <v>30.71999931335449</v>
@@ -3839,11 +3851,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>25.8292064666748</v>
+        <v>25.82920265197754</v>
       </c>
       <c r="C135" t="n">
         <v>34.18000030517578</v>
@@ -3868,11 +3880,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>25.54203987121582</v>
+        <v>25.54205131530762</v>
       </c>
       <c r="C136" t="n">
         <v>33.79999923706055</v>
@@ -3897,11 +3909,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>25.97036361694336</v>
+        <v>25.97036170959473</v>
       </c>
       <c r="C137" t="n">
         <v>34.06999969482422</v>
@@ -3926,11 +3938,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>24.03420829772949</v>
+        <v>24.03421592712402</v>
       </c>
       <c r="C138" t="n">
         <v>31.53000068664551</v>
@@ -3955,11 +3967,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>23.85889625549316</v>
+        <v>23.85889053344727</v>
       </c>
       <c r="C139" t="n">
         <v>31.29999923706055</v>
@@ -3984,7 +3996,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -4013,11 +4025,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>24.78194236755371</v>
+        <v>24.78193855285645</v>
       </c>
       <c r="C141" t="n">
         <v>32.20999908447266</v>
@@ -4042,11 +4054,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>25.87446594238281</v>
+        <v>25.87447547912598</v>
       </c>
       <c r="C142" t="n">
         <v>33.63000106811523</v>
@@ -4071,11 +4083,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>26.50159072875977</v>
+        <v>26.50160217285156</v>
       </c>
       <c r="C143" t="n">
         <v>34.15000152587891</v>
@@ -4100,11 +4112,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>28.94610404968262</v>
+        <v>28.94610595703125</v>
       </c>
       <c r="C144" t="n">
         <v>37.29999923706055</v>
@@ -4129,11 +4141,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>29.72214698791504</v>
+        <v>29.72213745117188</v>
       </c>
       <c r="C145" t="n">
         <v>38.29999923706055</v>
@@ -4158,11 +4170,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>32.4769401550293</v>
+        <v>32.47693252563477</v>
       </c>
       <c r="C146" t="n">
         <v>41.54000091552734</v>
@@ -4187,7 +4199,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>33.53240966796875</v>
+        <v>33.53240585327148</v>
       </c>
       <c r="C148" t="n">
         <v>42.88999938964844</v>
@@ -4241,11 +4253,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>34.90531158447266</v>
+        <v>34.90531921386719</v>
       </c>
       <c r="C149" t="n">
         <v>44.29000091552734</v>
@@ -4268,11 +4280,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>33.66011428833008</v>
+        <v>33.66010284423828</v>
       </c>
       <c r="C150" t="n">
         <v>42.70999908447266</v>
@@ -4295,11 +4307,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>33.91229248046875</v>
+        <v>33.91230392456055</v>
       </c>
       <c r="C151" t="n">
         <v>43.02999877929688</v>
@@ -4322,11 +4334,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>33.5888671875</v>
+        <v>33.58886337280273</v>
       </c>
       <c r="C152" t="n">
         <v>42.29000091552734</v>
@@ -4349,11 +4361,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>37.94135284423828</v>
+        <v>37.94136047363281</v>
       </c>
       <c r="C153" t="n">
         <v>47.77000045776367</v>
@@ -4376,11 +4388,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>38.64030456542969</v>
+        <v>38.64031219482422</v>
       </c>
       <c r="C154" t="n">
         <v>48.65000152587891</v>
@@ -4405,11 +4417,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>36.58266067504883</v>
+        <v>36.58265686035156</v>
       </c>
       <c r="C155" t="n">
         <v>45.75</v>
@@ -4434,11 +4446,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>38.2778434753418</v>
+        <v>38.27784729003906</v>
       </c>
       <c r="C156" t="n">
         <v>47.86999893188477</v>
@@ -4463,11 +4475,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>34.64756393432617</v>
+        <v>34.6475715637207</v>
       </c>
       <c r="C157" t="n">
         <v>43.33000183105469</v>
@@ -4492,11 +4504,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>38.10684204101562</v>
+        <v>38.10685729980469</v>
       </c>
       <c r="C158" t="n">
         <v>47.29000091552734</v>
@@ -4521,11 +4533,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>41.71688461303711</v>
+        <v>41.71689605712891</v>
       </c>
       <c r="C159" t="n">
         <v>51.77000045776367</v>
@@ -4550,11 +4562,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>43.50580215454102</v>
+        <v>43.50579071044922</v>
       </c>
       <c r="C160" t="n">
         <v>53.9900016784668</v>
@@ -4579,7 +4591,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4608,11 +4620,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>42.19184494018555</v>
+        <v>42.19184875488281</v>
       </c>
       <c r="C162" t="n">
         <v>52.02999877929688</v>
@@ -4637,11 +4649,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>44.38133239746094</v>
+        <v>44.38132858276367</v>
       </c>
       <c r="C163" t="n">
         <v>54.72999954223633</v>
@@ -4666,11 +4678,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>45.20814895629883</v>
+        <v>45.20815277099609</v>
       </c>
       <c r="C164" t="n">
         <v>55.40000152587891</v>
@@ -4695,7 +4707,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4724,7 +4736,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4753,11 +4765,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>39.06331253051758</v>
+        <v>39.06330490112305</v>
       </c>
       <c r="C167" t="n">
         <v>47.5099983215332</v>
@@ -4782,11 +4794,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>37.25443649291992</v>
+        <v>37.25442886352539</v>
       </c>
       <c r="C168" t="n">
         <v>45.31000137329102</v>
@@ -4811,11 +4823,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>39.43330383300781</v>
+        <v>39.43329238891602</v>
       </c>
       <c r="C169" t="n">
         <v>47.95999908447266</v>
@@ -4840,7 +4852,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4869,11 +4881,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>33.07228851318359</v>
+        <v>33.07229232788086</v>
       </c>
       <c r="C171" t="n">
         <v>39.93000030517578</v>
@@ -4898,11 +4910,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>32.55876922607422</v>
+        <v>32.55876541137695</v>
       </c>
       <c r="C172" t="n">
         <v>39.31000137329102</v>
@@ -4927,11 +4939,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>35.43433380126953</v>
+        <v>35.43432998657227</v>
       </c>
       <c r="C173" t="n">
         <v>42.38000106811523</v>
@@ -4956,7 +4968,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4985,11 +4997,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>38.99613952636719</v>
+        <v>38.99615478515625</v>
       </c>
       <c r="C175" t="n">
         <v>46.63999938964844</v>
@@ -5014,11 +5026,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>39.69097900390625</v>
+        <v>39.69098281860352</v>
       </c>
       <c r="C176" t="n">
         <v>47.09999847412109</v>
@@ -5043,11 +5055,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>35.57862091064453</v>
+        <v>35.57861328125</v>
       </c>
       <c r="C177" t="n">
         <v>42.22000122070312</v>
@@ -5072,11 +5084,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>33.19378662109375</v>
+        <v>33.19379806518555</v>
       </c>
       <c r="C178" t="n">
         <v>39.38999938964844</v>
@@ -5101,11 +5113,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>30.53183364868164</v>
+        <v>30.53182411193848</v>
       </c>
       <c r="C179" t="n">
         <v>35.90000152587891</v>
@@ -5130,11 +5142,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>36.58717346191406</v>
+        <v>36.587158203125</v>
       </c>
       <c r="C180" t="n">
         <v>43.02000045776367</v>
@@ -5159,11 +5171,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>38.0584831237793</v>
+        <v>38.05847930908203</v>
       </c>
       <c r="C181" t="n">
         <v>44.75</v>
@@ -5188,7 +5200,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5217,7 +5229,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5246,11 +5258,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>44.33439636230469</v>
+        <v>44.33439254760742</v>
       </c>
       <c r="C184" t="n">
         <v>51.70999908447266</v>
@@ -5275,11 +5287,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>43.96141815185547</v>
+        <v>43.96142578125</v>
       </c>
       <c r="C185" t="n">
         <v>50.90999984741211</v>
@@ -5304,11 +5316,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>45.67981719970703</v>
+        <v>45.67981338500977</v>
       </c>
       <c r="C186" t="n">
         <v>52.90000152587891</v>
@@ -5333,11 +5345,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>45.76616287231445</v>
+        <v>45.76616668701172</v>
       </c>
       <c r="C187" t="n">
         <v>53</v>
@@ -5362,11 +5374,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>48.14603424072266</v>
+        <v>48.14604187011719</v>
       </c>
       <c r="C188" t="n">
         <v>55.36999893188477</v>
@@ -5391,11 +5403,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>51.31983184814453</v>
+        <v>51.31983947753906</v>
       </c>
       <c r="C189" t="n">
         <v>59.02000045776367</v>
@@ -5420,11 +5432,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>47.32867431640625</v>
+        <v>47.32867813110352</v>
       </c>
       <c r="C190" t="n">
         <v>54.43000030517578</v>
@@ -5449,11 +5461,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>48.99653244018555</v>
+        <v>48.99653625488281</v>
       </c>
       <c r="C191" t="n">
         <v>55.97000122070312</v>
@@ -5478,11 +5490,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>48.00732421875</v>
+        <v>48.00732040405273</v>
       </c>
       <c r="C192" t="n">
         <v>54.84000015258789</v>
@@ -5507,11 +5519,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>55.47454833984375</v>
+        <v>55.47452926635742</v>
       </c>
       <c r="C193" t="n">
         <v>63.36999893188477</v>
@@ -5536,7 +5548,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5565,7 +5577,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5594,11 +5606,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>49.10032653808594</v>
+        <v>49.10033798217773</v>
       </c>
       <c r="C196" t="n">
         <v>55.7599983215332</v>
@@ -5623,11 +5635,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>43.42546463012695</v>
+        <v>43.42546081542969</v>
       </c>
       <c r="C197" t="n">
         <v>48.97999954223633</v>
@@ -5652,11 +5664,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>39.94113922119141</v>
+        <v>39.94114303588867</v>
       </c>
       <c r="C198" t="n">
         <v>45.04999923706055</v>
@@ -5681,11 +5693,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>37.80443572998047</v>
+        <v>37.804443359375</v>
       </c>
       <c r="C199" t="n">
         <v>42.63999938964844</v>
@@ -5710,7 +5722,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5739,7 +5751,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5768,7 +5780,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5797,11 +5809,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>41.01805877685547</v>
+        <v>41.01806259155273</v>
       </c>
       <c r="C203" t="n">
         <v>45.43000030517578</v>
@@ -5826,7 +5838,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5855,11 +5867,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>43.01343154907227</v>
+        <v>43.01344299316406</v>
       </c>
       <c r="C205" t="n">
         <v>47.63999938964844</v>
@@ -5884,7 +5896,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5913,11 +5925,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>44.06698608398438</v>
+        <v>44.06699371337891</v>
       </c>
       <c r="C207" t="n">
         <v>48.41999816894531</v>
@@ -5942,7 +5954,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5971,7 +5983,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6000,11 +6012,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>45.54417037963867</v>
+        <v>45.54416656494141</v>
       </c>
       <c r="C210" t="n">
         <v>49.66999816894531</v>
@@ -6029,7 +6041,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6058,11 +6070,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>48.07915878295898</v>
+        <v>48.07915115356445</v>
       </c>
       <c r="C212" t="n">
         <v>52.04000091552734</v>
@@ -6087,11 +6099,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>52.98500061035156</v>
+        <v>52.9849967956543</v>
       </c>
       <c r="C213" t="n">
         <v>57.34999847412109</v>
@@ -6116,11 +6128,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>49.66823959350586</v>
+        <v>49.66823577880859</v>
       </c>
       <c r="C214" t="n">
         <v>53.7599983215332</v>
@@ -6145,11 +6157,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>48.51013946533203</v>
+        <v>48.51013565063477</v>
       </c>
       <c r="C215" t="n">
         <v>52.13000106811523</v>
@@ -6174,11 +6186,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>45.02053451538086</v>
+        <v>45.02053070068359</v>
       </c>
       <c r="C216" t="n">
         <v>48.38000106811523</v>
@@ -6203,7 +6215,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6232,7 +6244,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6261,11 +6273,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>45.36148071289062</v>
+        <v>45.36146926879883</v>
       </c>
       <c r="C219" t="n">
         <v>48.36999893188477</v>
@@ -6290,11 +6302,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>46.80569458007812</v>
+        <v>46.80569076538086</v>
       </c>
       <c r="C220" t="n">
         <v>49.90999984741211</v>
@@ -6319,11 +6331,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>44.41787719726562</v>
+        <v>44.41788864135742</v>
       </c>
       <c r="C221" t="n">
         <v>46.97999954223633</v>
@@ -6348,11 +6360,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>43.96405410766602</v>
+        <v>43.96405792236328</v>
       </c>
       <c r="C222" t="n">
         <v>46.5</v>
@@ -6377,11 +6389,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>44.91897201538086</v>
+        <v>44.91897964477539</v>
       </c>
       <c r="C223" t="n">
         <v>47.5099983215332</v>
@@ -6406,11 +6418,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>46.20015335083008</v>
+        <v>46.20015716552734</v>
       </c>
       <c r="C224" t="n">
         <v>48.45000076293945</v>
@@ -6435,11 +6447,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>48.1931037902832</v>
+        <v>48.19309997558594</v>
       </c>
       <c r="C225" t="n">
         <v>50.54000091552734</v>
@@ -6464,7 +6476,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6493,7 +6505,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6522,11 +6534,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>56.89199447631836</v>
+        <v>56.89199066162109</v>
       </c>
       <c r="C228" t="n">
         <v>59.20999908447266</v>
@@ -6551,7 +6563,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6580,11 +6592,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>58.62434768676758</v>
+        <v>58.62435150146484</v>
       </c>
       <c r="C230" t="n">
         <v>60.59999847412109</v>
@@ -6609,7 +6621,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6638,7 +6650,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6667,11 +6679,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>56.22077941894531</v>
+        <v>56.22078704833984</v>
       </c>
       <c r="C233" t="n">
         <v>57.72999954223633</v>
@@ -6696,7 +6708,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6725,11 +6737,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>67.56623077392578</v>
+        <v>67.56621551513672</v>
       </c>
       <c r="C235" t="n">
         <v>69.37999725341797</v>
@@ -6754,7 +6766,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6783,11 +6795,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>67.68841552734375</v>
+        <v>67.68840789794922</v>
       </c>
       <c r="C237" t="n">
         <v>69.08999633789062</v>
@@ -6812,11 +6824,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>67.03201293945312</v>
+        <v>67.03200531005859</v>
       </c>
       <c r="C238" t="n">
         <v>68.41999816894531</v>
@@ -6841,7 +6853,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6870,7 +6882,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6899,7 +6911,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6928,7 +6940,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6957,7 +6969,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6986,7 +6998,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7015,7 +7027,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7044,7 +7056,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7073,7 +7085,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7102,7 +7114,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7131,7 +7143,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7160,32 +7172,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>106.4300003051758</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="C250" t="n">
-        <v>106.4300003051758</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="D250" t="n">
-        <v>276583600</v>
+        <v>308944000</v>
       </c>
       <c r="E250" t="n">
         <v>3.33</v>
       </c>
       <c r="F250" t="n">
-        <v>31.96096105260534</v>
+        <v>32.12312348970064</v>
       </c>
       <c r="G250" t="n">
         <v>3942586873</v>
       </c>
       <c r="H250" t="n">
-        <v>419609522096.572</v>
+        <v>421738522617.5381</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07015282323748558</v>
+        <v>0.07836073368877165</v>
       </c>
     </row>
   </sheetData>
@@ -7217,75 +7229,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39656</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39746</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40135</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7321,13 +7333,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39747</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39837</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40226</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7363,13 +7375,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39838</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39928</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40324</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39929</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40019</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40442</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7438,7 +7450,7 @@
       <c r="I5" t="n">
         <v>1.051694740460639</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40442</v>
       </c>
       <c r="K5" t="n">
@@ -7451,13 +7463,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40020</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40110</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40135</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7484,7 +7496,7 @@
       <c r="I6" t="n">
         <v>0.9816947404606394</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40442</v>
       </c>
       <c r="K6" t="n">
@@ -7497,13 +7509,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40111</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40201</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40226</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7530,7 +7542,7 @@
       <c r="I7" t="n">
         <v>1.041694740460639</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40442</v>
       </c>
       <c r="K7" t="n">
@@ -7543,13 +7555,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40202</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40324</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7576,7 +7588,7 @@
       <c r="I8" t="n">
         <v>1.18</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40442</v>
       </c>
       <c r="K8" t="n">
@@ -7589,13 +7601,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40300</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40442</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7622,7 +7634,7 @@
       <c r="I9" t="n">
         <v>1.32</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40442</v>
       </c>
       <c r="K9" t="n">
@@ -7635,13 +7647,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40481</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7668,7 +7680,7 @@
       <c r="I10" t="n">
         <v>1.36</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="K10" t="n">
@@ -7681,13 +7693,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40572</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7714,7 +7726,7 @@
       <c r="I11" t="n">
         <v>1.31</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K11" t="n">
@@ -7727,13 +7739,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40573</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40688</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7760,7 +7772,7 @@
       <c r="I12" t="n">
         <v>1.27</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40688</v>
       </c>
       <c r="K12" t="n">
@@ -7773,13 +7785,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40754</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40800</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7806,7 +7818,7 @@
       <c r="I13" t="n">
         <v>1.16</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40800</v>
       </c>
       <c r="K13" t="n">
@@ -7819,13 +7831,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40845</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40869</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7852,7 +7864,7 @@
       <c r="I14" t="n">
         <v>1.15</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40869</v>
       </c>
       <c r="K14" t="n">
@@ -7865,13 +7877,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40846</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40936</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7898,7 +7910,7 @@
       <c r="I15" t="n">
         <v>1.28</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="K15" t="n">
@@ -7911,13 +7923,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40937</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41027</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41052</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7944,7 +7956,7 @@
       <c r="I16" t="n">
         <v>1.35</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41052</v>
       </c>
       <c r="K16" t="n">
@@ -7957,13 +7969,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41028</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41118</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41164</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7990,7 +8002,7 @@
       <c r="I17" t="n">
         <v>1.49</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41164</v>
       </c>
       <c r="K17" t="n">
@@ -8003,13 +8015,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41119</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41209</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41233</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8036,7 +8048,7 @@
       <c r="I18" t="n">
         <v>1.55</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41233</v>
       </c>
       <c r="K18" t="n">
@@ -8049,13 +8061,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41210</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41300</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8082,7 +8094,7 @@
       <c r="I19" t="n">
         <v>1.74</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="K19" t="n">
@@ -8095,13 +8107,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41301</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41391</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41415</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8128,7 +8140,7 @@
       <c r="I20" t="n">
         <v>1.8</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41415</v>
       </c>
       <c r="K20" t="n">
@@ -8141,13 +8153,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41392</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41482</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41527</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8174,7 +8186,7 @@
       <c r="I21" t="n">
         <v>1.86</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41527</v>
       </c>
       <c r="K21" t="n">
@@ -8187,13 +8199,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41483</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41573</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41600</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8220,7 +8232,7 @@
       <c r="I22" t="n">
         <v>1.84</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41600</v>
       </c>
       <c r="K22" t="n">
@@ -8233,13 +8245,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41574</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41664</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8266,7 +8278,7 @@
       <c r="I23" t="n">
         <v>1.52</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="K23" t="n">
@@ -8279,13 +8291,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41665</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41755</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41781</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8312,7 +8324,7 @@
       <c r="I24" t="n">
         <v>1.48</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41781</v>
       </c>
       <c r="K24" t="n">
@@ -8325,13 +8337,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41756</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41846</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41891</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8358,7 +8370,7 @@
       <c r="I25" t="n">
         <v>1.49</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41891</v>
       </c>
       <c r="K25" t="n">
@@ -8371,13 +8383,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41847</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41937</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41963</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8404,7 +8416,7 @@
       <c r="I26" t="n">
         <v>1.47</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41963</v>
       </c>
       <c r="K26" t="n">
@@ -8417,13 +8429,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41938</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42028</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42053</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8450,7 +8462,7 @@
       <c r="I27" t="n">
         <v>1.66</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42053</v>
       </c>
       <c r="K27" t="n">
@@ -8463,13 +8475,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42029</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42119</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42144</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8496,7 +8508,7 @@
       <c r="I28" t="n">
         <v>1.71</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42144</v>
       </c>
       <c r="K28" t="n">
@@ -8509,13 +8521,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42120</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42210</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42255</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8542,7 +8554,7 @@
       <c r="I29" t="n">
         <v>1.75</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42255</v>
       </c>
       <c r="K29" t="n">
@@ -8555,13 +8567,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42211</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42301</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42327</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8588,7 +8600,7 @@
       <c r="I30" t="n">
         <v>1.88</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42327</v>
       </c>
       <c r="K30" t="n">
@@ -8601,13 +8613,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42302</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42392</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8634,7 +8646,7 @@
       <c r="I31" t="n">
         <v>2.04</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="K31" t="n">
@@ -8647,13 +8659,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42393</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42514</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8680,7 +8692,7 @@
       <c r="I32" t="n">
         <v>2.03</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42514</v>
       </c>
       <c r="K32" t="n">
@@ -8693,13 +8705,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42581</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42621</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8726,7 +8738,7 @@
       <c r="I33" t="n">
         <v>2.109999999999999</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42621</v>
       </c>
       <c r="K33" t="n">
@@ -8739,13 +8751,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42672</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42696</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8772,7 +8784,7 @@
       <c r="I34" t="n">
         <v>2.09</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42696</v>
       </c>
       <c r="K34" t="n">
@@ -8785,13 +8797,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42673</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42763</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8818,7 +8830,7 @@
       <c r="I35" t="n">
         <v>1.94</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="K35" t="n">
@@ -8831,13 +8843,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42764</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42854</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42878</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8864,7 +8876,7 @@
       <c r="I36" t="n">
         <v>1.98</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42878</v>
       </c>
       <c r="K36" t="n">
@@ -8877,13 +8889,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42945</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42985</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8910,7 +8922,7 @@
       <c r="I37" t="n">
         <v>1.91</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42985</v>
       </c>
       <c r="K37" t="n">
@@ -8923,13 +8935,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42946</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43036</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43060</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8956,7 +8968,7 @@
       <c r="I38" t="n">
         <v>1.93</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43060</v>
       </c>
       <c r="K38" t="n">
@@ -8969,13 +8981,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43037</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43127</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9002,7 +9014,7 @@
       <c r="I39" t="n">
         <v>-0.3200000000000001</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K39" t="n">
@@ -9015,13 +9027,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43128</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43218</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43242</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9048,7 +9060,7 @@
       <c r="I40" t="n">
         <v>-0.26</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43242</v>
       </c>
       <c r="K40" t="n">
@@ -9061,13 +9073,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43219</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43309</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43349</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9094,7 +9106,7 @@
       <c r="I41" t="n">
         <v>0.07000000000000006</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43349</v>
       </c>
       <c r="K41" t="n">
@@ -9107,13 +9119,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43310</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43400</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43424</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9140,7 +9152,7 @@
       <c r="I42" t="n">
         <v>0.3600000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43424</v>
       </c>
       <c r="K42" t="n">
@@ -9153,13 +9165,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43401</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43491</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9186,7 +9198,7 @@
       <c r="I43" t="n">
         <v>2.77</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="K43" t="n">
@@ -9199,13 +9211,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43492</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43582</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43606</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9232,7 +9244,7 @@
       <c r="I44" t="n">
         <v>2.9</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43606</v>
       </c>
       <c r="K44" t="n">
@@ -9245,13 +9257,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43583</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43673</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43713</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9278,7 +9290,7 @@
       <c r="I45" t="n">
         <v>2.6</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43713</v>
       </c>
       <c r="K45" t="n">
@@ -9291,13 +9303,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43674</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43764</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43788</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9324,7 +9336,7 @@
       <c r="I46" t="n">
         <v>2.51</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43788</v>
       </c>
       <c r="K46" t="n">
@@ -9337,13 +9349,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43765</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43855</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43879</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9370,7 +9382,7 @@
       <c r="I47" t="n">
         <v>2.56</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43879</v>
       </c>
       <c r="K47" t="n">
@@ -9383,13 +9395,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43856</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43946</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43969</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9416,7 +9428,7 @@
       <c r="I48" t="n">
         <v>2.52</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43969</v>
       </c>
       <c r="K48" t="n">
@@ -9429,13 +9441,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43947</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44037</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44077</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9462,7 +9474,7 @@
       <c r="I49" t="n">
         <v>2.63</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44077</v>
       </c>
       <c r="K49" t="n">
@@ -9475,13 +9487,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44038</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44128</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44152</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9508,7 +9520,7 @@
       <c r="I50" t="n">
         <v>2.46</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44152</v>
       </c>
       <c r="K50" t="n">
@@ -9521,13 +9533,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44129</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44219</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44243</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9554,7 +9566,7 @@
       <c r="I51" t="n">
         <v>2.38</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44243</v>
       </c>
       <c r="K51" t="n">
@@ -9567,13 +9579,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44220</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44341</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9600,7 +9612,7 @@
       <c r="I52" t="n">
         <v>2.41</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44341</v>
       </c>
       <c r="K52" t="n">
@@ -9613,13 +9625,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44318</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44448</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9646,7 +9658,7 @@
       <c r="I53" t="n">
         <v>2.5</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44448</v>
       </c>
       <c r="K53" t="n">
@@ -9659,13 +9671,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44499</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44523</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9692,7 +9704,7 @@
       <c r="I54" t="n">
         <v>2.69</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44523</v>
       </c>
       <c r="K54" t="n">
@@ -9705,13 +9717,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44590</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9738,7 +9750,7 @@
       <c r="I55" t="n">
         <v>2.8</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K55" t="n">
@@ -9751,13 +9763,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44591</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44706</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9784,7 +9796,7 @@
       <c r="I56" t="n">
         <v>2.85</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44706</v>
       </c>
       <c r="K56" t="n">
@@ -9797,13 +9809,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44772</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44812</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9830,7 +9842,7 @@
       <c r="I57" t="n">
         <v>2.82</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44812</v>
       </c>
       <c r="K57" t="n">
@@ -9843,13 +9855,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44863</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44887</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9876,7 +9888,7 @@
       <c r="I58" t="n">
         <v>2.77</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44887</v>
       </c>
       <c r="K58" t="n">
@@ -9889,13 +9901,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44864</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44954</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9922,7 +9934,7 @@
       <c r="I59" t="n">
         <v>2.73</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="K59" t="n">
@@ -9935,13 +9947,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44955</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45045</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45070</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9968,7 +9980,7 @@
       <c r="I60" t="n">
         <v>2.78</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45070</v>
       </c>
       <c r="K60" t="n">
@@ -9981,13 +9993,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45136</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45176</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10014,7 +10026,7 @@
       <c r="I61" t="n">
         <v>3.07</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45176</v>
       </c>
       <c r="K61" t="n">
@@ -10027,13 +10039,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45137</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45227</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10060,7 +10072,7 @@
       <c r="I62" t="n">
         <v>3.31</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="K62" t="n">
@@ -10073,13 +10085,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45228</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45318</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10106,7 +10118,7 @@
       <c r="I63" t="n">
         <v>3.29</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="K63" t="n">
@@ -10119,13 +10131,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45319</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45409</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45433</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10152,7 +10164,7 @@
       <c r="I64" t="n">
         <v>2.97</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45433</v>
       </c>
       <c r="K64" t="n">
@@ -10165,13 +10177,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45410</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45500</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45540</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10198,7 +10210,7 @@
       <c r="I65" t="n">
         <v>2.54</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45540</v>
       </c>
       <c r="K65" t="n">
@@ -10211,13 +10223,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45501</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45591</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45615</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10244,7 +10256,7 @@
       <c r="I66" t="n">
         <v>2.33</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45615</v>
       </c>
       <c r="K66" t="n">
@@ -10257,13 +10269,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45592</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45682</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10290,7 +10302,7 @@
       <c r="I67" t="n">
         <v>2.29</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="K67" t="n">
@@ -10303,13 +10315,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45683</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45773</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10336,7 +10348,7 @@
       <c r="I68" t="n">
         <v>2.45</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="K68" t="n">
@@ -10349,13 +10361,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45774</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45864</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10382,7 +10394,7 @@
       <c r="I69" t="n">
         <v>2.55</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="K69" t="n">
@@ -10395,13 +10407,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45865</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45955</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10428,7 +10440,7 @@
       <c r="I70" t="n">
         <v>2.589999999999999</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="K70" t="n">
@@ -10441,13 +10453,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45956</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46046</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10474,7 +10486,7 @@
       <c r="I71" t="n">
         <v>2.78</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="K71" t="n">
@@ -10487,13 +10499,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46047</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10520,7 +10532,7 @@
       <c r="I72" t="n">
         <v>3.01</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="K72" t="n">
@@ -10533,13 +10545,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46228</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46267</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10566,7 +10578,7 @@
       <c r="I73" t="n">
         <v>3.33</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46267</v>
       </c>
       <c r="K73" t="n">
@@ -10603,52 +10615,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40129</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40135</v>
       </c>
       <c r="C2" t="n">
@@ -10677,10 +10689,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40220</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40226</v>
       </c>
       <c r="C3" t="n">
@@ -10709,10 +10721,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40318</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40324</v>
       </c>
       <c r="C4" t="n">
@@ -10741,10 +10753,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40436</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40442</v>
       </c>
       <c r="C5" t="n">
@@ -10773,10 +10785,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40500</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40505</v>
       </c>
       <c r="C6" t="n">
@@ -10805,10 +10817,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40591</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="C7" t="n">
@@ -10837,10 +10849,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40681</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40688</v>
       </c>
       <c r="C8" t="n">
@@ -10869,10 +10881,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40794</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40800</v>
       </c>
       <c r="C9" t="n">
@@ -10901,10 +10913,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40862</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40869</v>
       </c>
       <c r="C10" t="n">
@@ -10933,10 +10945,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40953</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="C11" t="n">
@@ -10965,10 +10977,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41047</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41052</v>
       </c>
       <c r="C12" t="n">
@@ -10997,10 +11009,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41157</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41164</v>
       </c>
       <c r="C13" t="n">
@@ -11029,10 +11041,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41228</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41233</v>
       </c>
       <c r="C14" t="n">
@@ -11061,10 +11073,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41319</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="C15" t="n">
@@ -11093,10 +11105,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41410</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41415</v>
       </c>
       <c r="C16" t="n">
@@ -11125,10 +11137,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41521</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41527</v>
       </c>
       <c r="C17" t="n">
@@ -11157,10 +11169,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41593</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41600</v>
       </c>
       <c r="C18" t="n">
@@ -11189,10 +11201,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="C19" t="n">
@@ -11221,10 +11233,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41775</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41781</v>
       </c>
       <c r="C20" t="n">
@@ -11253,10 +11265,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41886</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41891</v>
       </c>
       <c r="C21" t="n">
@@ -11285,10 +11297,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41957</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41963</v>
       </c>
       <c r="C22" t="n">
@@ -11317,10 +11329,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42048</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42053</v>
       </c>
       <c r="C23" t="n">
@@ -11349,10 +11361,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42139</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42144</v>
       </c>
       <c r="C24" t="n">
@@ -11381,10 +11393,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42250</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42255</v>
       </c>
       <c r="C25" t="n">
@@ -11413,10 +11425,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42321</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42327</v>
       </c>
       <c r="C26" t="n">
@@ -11445,10 +11457,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42412</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="C27" t="n">
@@ -11477,10 +11489,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42509</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42514</v>
       </c>
       <c r="C28" t="n">
@@ -11509,10 +11521,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42615</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42621</v>
       </c>
       <c r="C29" t="n">
@@ -11541,10 +11553,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42691</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42696</v>
       </c>
       <c r="C30" t="n">
@@ -11573,10 +11585,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42782</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="C31" t="n">
@@ -11605,10 +11617,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42873</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42878</v>
       </c>
       <c r="C32" t="n">
@@ -11637,10 +11649,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42979</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42985</v>
       </c>
       <c r="C33" t="n">
@@ -11669,10 +11681,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43055</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43060</v>
       </c>
       <c r="C34" t="n">
@@ -11701,10 +11713,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43146</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="C35" t="n">
@@ -11733,10 +11745,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43237</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43242</v>
       </c>
       <c r="C36" t="n">
@@ -11765,10 +11777,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43343</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43349</v>
       </c>
       <c r="C37" t="n">
@@ -11797,10 +11809,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43419</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43424</v>
       </c>
       <c r="C38" t="n">
@@ -11829,10 +11841,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43510</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="C39" t="n">
@@ -11861,10 +11873,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43601</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43606</v>
       </c>
       <c r="C40" t="n">
@@ -11893,10 +11905,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43707</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43713</v>
       </c>
       <c r="C41" t="n">
@@ -11925,10 +11937,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43783</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43788</v>
       </c>
       <c r="C42" t="n">
@@ -11957,10 +11969,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43874</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43879</v>
       </c>
       <c r="C43" t="n">
@@ -11989,10 +12001,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43965</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43969</v>
       </c>
       <c r="C44" t="n">
@@ -12021,10 +12033,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44071</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44077</v>
       </c>
       <c r="C45" t="n">
@@ -12053,10 +12065,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44147</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44152</v>
       </c>
       <c r="C46" t="n">
@@ -12085,10 +12097,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44238</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44243</v>
       </c>
       <c r="C47" t="n">
@@ -12117,10 +12129,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44336</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44341</v>
       </c>
       <c r="C48" t="n">
@@ -12149,10 +12161,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44442</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44448</v>
       </c>
       <c r="C49" t="n">
@@ -12181,10 +12193,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44518</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44523</v>
       </c>
       <c r="C50" t="n">
@@ -12213,10 +12225,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44609</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="C51" t="n">
@@ -12245,10 +12257,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44700</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44706</v>
       </c>
       <c r="C52" t="n">
@@ -12277,10 +12289,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44806</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44812</v>
       </c>
       <c r="C53" t="n">
@@ -12309,10 +12321,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44882</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44887</v>
       </c>
       <c r="C54" t="n">
@@ -12341,10 +12353,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44973</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="C55" t="n">
@@ -12373,10 +12385,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45064</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45070</v>
       </c>
       <c r="C56" t="n">
@@ -12405,10 +12417,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45170</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45176</v>
       </c>
       <c r="C57" t="n">
@@ -12437,10 +12449,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45246</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="C58" t="n">
@@ -12469,10 +12481,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45337</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="C59" t="n">
@@ -12501,10 +12513,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45428</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45433</v>
       </c>
       <c r="C60" t="n">
@@ -12533,10 +12545,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45534</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45540</v>
       </c>
       <c r="C61" t="n">
@@ -12565,10 +12577,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45610</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45615</v>
       </c>
       <c r="C62" t="n">
@@ -12597,10 +12609,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45701</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="C63" t="n">
@@ -12629,10 +12641,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45792</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="C64" t="n">
@@ -12661,10 +12673,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45897</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="C65" t="n">
@@ -12693,10 +12705,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45974</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="C66" t="n">
@@ -12725,10 +12737,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46065</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="C67" t="n">
@@ -12757,10 +12769,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46156</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="C68" t="n">
@@ -12789,10 +12801,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46261</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46267</v>
       </c>
       <c r="C69" t="n">
@@ -12839,12 +12851,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/CSCO.xlsx
+++ b/salidas/empresas/CSCO.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>11.9064416885376</v>
+        <v>11.90644550323486</v>
       </c>
       <c r="C2" t="n">
         <v>18.56999969482422</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>12.97718811035156</v>
+        <v>12.97719287872314</v>
       </c>
       <c r="C3" t="n">
         <v>20.23999977111816</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>13.89405632019043</v>
+        <v>13.89405822753906</v>
       </c>
       <c r="C4" t="n">
         <v>21.67000007629395</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>13.43241882324219</v>
+        <v>13.43241691589355</v>
       </c>
       <c r="C5" t="n">
         <v>20.95000076293945</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>12.61813640594482</v>
+        <v>12.61814212799072</v>
       </c>
       <c r="C6" t="n">
         <v>19.68000030517578</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>12.52196502685547</v>
+        <v>12.5219669342041</v>
       </c>
       <c r="C7" t="n">
         <v>19.53000068664551</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>11.46403884887695</v>
+        <v>11.46403694152832</v>
       </c>
       <c r="C8" t="n">
         <v>17.8799991607666</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>14.09923076629639</v>
+        <v>14.09922790527344</v>
       </c>
       <c r="C9" t="n">
         <v>21.98999977111816</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.73398208618164</v>
+        <v>14.73397827148438</v>
       </c>
       <c r="C10" t="n">
         <v>22.97999954223633</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>17.25376129150391</v>
+        <v>17.2537727355957</v>
       </c>
       <c r="C12" t="n">
         <v>26.90999984741211</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>17.5230541229248</v>
+        <v>17.52305221557617</v>
       </c>
       <c r="C13" t="n">
         <v>27.32999992370605</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>16.63183403015137</v>
+        <v>16.6318416595459</v>
       </c>
       <c r="C15" t="n">
         <v>25.94000053405762</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>16.36895751953125</v>
+        <v>16.36895179748535</v>
       </c>
       <c r="C16" t="n">
         <v>25.53000068664551</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>17.14477729797363</v>
+        <v>17.14476013183594</v>
       </c>
       <c r="C17" t="n">
         <v>26.73999977111816</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>17.85645484924316</v>
+        <v>17.85645866394043</v>
       </c>
       <c r="C19" t="n">
         <v>27.85000038146973</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>18.53610038757324</v>
+        <v>18.53609466552734</v>
       </c>
       <c r="C20" t="n">
         <v>28.90999984741211</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>20.46600151062012</v>
+        <v>20.46599960327148</v>
       </c>
       <c r="C21" t="n">
         <v>31.92000007629395</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>21.19692993164062</v>
+        <v>21.19693756103516</v>
       </c>
       <c r="C23" t="n">
         <v>33.06000137329102</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>17.96545600891113</v>
+        <v>17.9654541015625</v>
       </c>
       <c r="C24" t="n">
         <v>28.02000045776367</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>17.35635185241699</v>
+        <v>17.35635566711426</v>
       </c>
       <c r="C25" t="n">
         <v>27.06999969482422</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>15.70855522155762</v>
+        <v>15.70855712890625</v>
       </c>
       <c r="C26" t="n">
         <v>24.5</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.44567775726318</v>
+        <v>15.44568157196045</v>
       </c>
       <c r="C28" t="n">
         <v>24.09000015258789</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>16.43949317932129</v>
+        <v>16.43949127197266</v>
       </c>
       <c r="C29" t="n">
         <v>25.63999938964844</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>17.1319408416748</v>
+        <v>17.13195037841797</v>
       </c>
       <c r="C30" t="n">
         <v>26.71999931335449</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>14.91351318359375</v>
+        <v>14.91351890563965</v>
       </c>
       <c r="C31" t="n">
         <v>23.26000022888184</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>14.09923076629639</v>
+        <v>14.09922790527344</v>
       </c>
       <c r="C32" t="n">
         <v>21.98999977111816</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>15.42002964019775</v>
+        <v>15.42003440856934</v>
       </c>
       <c r="C33" t="n">
         <v>24.04999923706055</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>14.46469688415527</v>
+        <v>14.46469402313232</v>
       </c>
       <c r="C34" t="n">
         <v>22.55999946594238</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>10.60487842559814</v>
+        <v>10.60487937927246</v>
       </c>
       <c r="C36" t="n">
         <v>16.54000091552734</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>10.45099925994873</v>
+        <v>10.45100021362305</v>
       </c>
       <c r="C37" t="n">
         <v>16.29999923706055</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>9.598246574401855</v>
+        <v>9.598249435424805</v>
       </c>
       <c r="C38" t="n">
         <v>14.97000026702881</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>9.341781616210938</v>
+        <v>9.341780662536621</v>
       </c>
       <c r="C39" t="n">
         <v>14.56999969482422</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>10.75235271453857</v>
+        <v>10.75234699249268</v>
       </c>
       <c r="C40" t="n">
         <v>16.77000045776367</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>11.8615608215332</v>
+        <v>11.8615665435791</v>
       </c>
       <c r="C42" t="n">
         <v>18.5</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>14.11205577850342</v>
+        <v>14.11205196380615</v>
       </c>
       <c r="C44" t="n">
         <v>22.01000022888184</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>14.62498092651367</v>
+        <v>14.6249828338623</v>
       </c>
       <c r="C47" t="n">
         <v>22.80999946594238</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>15.00326919555664</v>
+        <v>15.00327777862549</v>
       </c>
       <c r="C48" t="n">
         <v>23.39999961853027</v>
@@ -1397,7 +1397,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>15.34950351715088</v>
+        <v>15.34950160980225</v>
       </c>
       <c r="C49" t="n">
         <v>23.94000053405762</v>
@@ -1422,7 +1422,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>14.40698623657227</v>
+        <v>14.40698909759521</v>
       </c>
       <c r="C50" t="n">
         <v>22.46999931335449</v>
@@ -1447,7 +1447,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>15.59955883026123</v>
+        <v>15.5995626449585</v>
       </c>
       <c r="C51" t="n">
         <v>24.32999992370605</v>
@@ -1497,7 +1497,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>17.26658821105957</v>
+        <v>17.26658630371094</v>
       </c>
       <c r="C53" t="n">
         <v>26.93000030517578</v>
@@ -1522,7 +1522,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>14.84939098358154</v>
+        <v>14.84938907623291</v>
       </c>
       <c r="C54" t="n">
         <v>23.15999984741211</v>
@@ -1547,7 +1547,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>13.66323661804199</v>
+        <v>13.66323566436768</v>
       </c>
       <c r="C55" t="n">
         <v>21.30999946594238</v>
@@ -1572,7 +1572,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>14.79169368743896</v>
+        <v>14.7916898727417</v>
       </c>
       <c r="C56" t="n">
         <v>23.06999969482422</v>
@@ -1597,7 +1597,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>12.81689739227295</v>
+        <v>12.81689548492432</v>
       </c>
       <c r="C57" t="n">
         <v>19.98999977111816</v>
@@ -1622,7 +1622,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>14.04152488708496</v>
+        <v>14.04152774810791</v>
       </c>
       <c r="C58" t="n">
         <v>21.89999961853027</v>
@@ -1651,7 +1651,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>14.65704536437988</v>
+        <v>14.65704154968262</v>
       </c>
       <c r="C59" t="n">
         <v>22.86000061035156</v>
@@ -1680,7 +1680,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>12.28473377227783</v>
+        <v>12.28473567962646</v>
       </c>
       <c r="C60" t="n">
         <v>19.15999984741211</v>
@@ -1709,7 +1709,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>12.97077941894531</v>
+        <v>12.97077655792236</v>
       </c>
       <c r="C61" t="n">
         <v>20.22999954223633</v>
@@ -1738,7 +1738,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>13.56065082550049</v>
+        <v>13.56064701080322</v>
       </c>
       <c r="C62" t="n">
         <v>21.14999961853027</v>
@@ -1767,7 +1767,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>11.90003204345703</v>
+        <v>11.90002822875977</v>
       </c>
       <c r="C63" t="n">
         <v>18.55999946594238</v>
@@ -1796,7 +1796,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>11.03450298309326</v>
+        <v>11.03450584411621</v>
       </c>
       <c r="C64" t="n">
         <v>17.14999961853027</v>
@@ -1825,7 +1825,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>11.27256298065186</v>
+        <v>11.27256488800049</v>
       </c>
       <c r="C65" t="n">
         <v>17.52000045776367</v>
@@ -1854,7 +1854,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.80930709838867</v>
+        <v>10.80931091308594</v>
       </c>
       <c r="C66" t="n">
         <v>16.79999923706055</v>
@@ -1883,7 +1883,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>10.04365062713623</v>
+        <v>10.04365158081055</v>
       </c>
       <c r="C67" t="n">
         <v>15.60999965667725</v>
@@ -1941,7 +1941,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>10.12053966522217</v>
+        <v>10.1205415725708</v>
       </c>
       <c r="C69" t="n">
         <v>15.67000007629395</v>
@@ -1970,7 +1970,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>10.01074695587158</v>
+        <v>10.01074600219727</v>
       </c>
       <c r="C70" t="n">
         <v>15.5</v>
@@ -1999,7 +1999,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>12.01514434814453</v>
+        <v>12.01514720916748</v>
       </c>
       <c r="C71" t="n">
         <v>18.53000068664551</v>
@@ -2028,7 +2028,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>12.08647155761719</v>
+        <v>12.08646583557129</v>
       </c>
       <c r="C72" t="n">
         <v>18.63999938964844</v>
@@ -2057,7 +2057,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>11.72335720062256</v>
+        <v>11.72336006164551</v>
       </c>
       <c r="C73" t="n">
         <v>18.07999992370605</v>
@@ -2086,7 +2086,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>12.7837963104248</v>
+        <v>12.78379249572754</v>
       </c>
       <c r="C74" t="n">
         <v>19.64999961853027</v>
@@ -2115,7 +2115,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>12.93342781066895</v>
+        <v>12.93342971801758</v>
       </c>
       <c r="C75" t="n">
         <v>19.8799991607666</v>
@@ -2144,7 +2144,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>13.75965881347656</v>
+        <v>13.75965118408203</v>
       </c>
       <c r="C76" t="n">
         <v>21.14999961853027</v>
@@ -2173,7 +2173,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>13.16529560089111</v>
+        <v>13.16529178619385</v>
       </c>
       <c r="C77" t="n">
         <v>20.15999984741211</v>
@@ -2202,7 +2202,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>10.66414928436279</v>
+        <v>10.66415023803711</v>
       </c>
       <c r="C78" t="n">
         <v>16.32999992370605</v>
@@ -2231,7 +2231,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>11.2127046585083</v>
+        <v>11.21270179748535</v>
       </c>
       <c r="C79" t="n">
         <v>17.17000007629395</v>
@@ -2260,7 +2260,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>10.46475315093994</v>
+        <v>10.46475410461426</v>
       </c>
       <c r="C80" t="n">
         <v>15.94999980926514</v>
@@ -2289,7 +2289,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>12.51833534240723</v>
+        <v>12.51834106445312</v>
       </c>
       <c r="C81" t="n">
         <v>19.07999992370605</v>
@@ -2318,7 +2318,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>12.53145313262939</v>
+        <v>12.53145599365234</v>
       </c>
       <c r="C82" t="n">
         <v>19.10000038146973</v>
@@ -2347,7 +2347,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>11.33541870117188</v>
+        <v>11.33541393280029</v>
       </c>
       <c r="C83" t="n">
         <v>17.14999961853027</v>
@@ -2376,7 +2376,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>12.59118461608887</v>
+        <v>12.59119129180908</v>
       </c>
       <c r="C84" t="n">
         <v>18.90999984741211</v>
@@ -2405,7 +2405,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>13.0839147567749</v>
+        <v>13.08391189575195</v>
       </c>
       <c r="C85" t="n">
         <v>19.64999961853027</v>
@@ -2434,7 +2434,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>13.69649600982666</v>
+        <v>13.69649505615234</v>
       </c>
       <c r="C86" t="n">
         <v>20.56999969482422</v>
@@ -2463,7 +2463,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>13.88958930969238</v>
+        <v>13.88958644866943</v>
       </c>
       <c r="C87" t="n">
         <v>20.86000061035156</v>
@@ -2492,7 +2492,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>13.91622924804688</v>
+        <v>13.91622352600098</v>
       </c>
       <c r="C88" t="n">
         <v>20.89999961853027</v>
@@ -2521,7 +2521,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>14.04214668273926</v>
+        <v>14.04213809967041</v>
       </c>
       <c r="C89" t="n">
         <v>20.92000007629395</v>
@@ -2550,7 +2550,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>16.19007873535156</v>
+        <v>16.1900806427002</v>
       </c>
       <c r="C90" t="n">
         <v>24.1200008392334</v>
@@ -2579,7 +2579,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>16.33775520324707</v>
+        <v>16.33775901794434</v>
       </c>
       <c r="C91" t="n">
         <v>24.34000015258789</v>
@@ -2608,7 +2608,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>17.297607421875</v>
+        <v>17.2976131439209</v>
       </c>
       <c r="C92" t="n">
         <v>25.59000015258789</v>
@@ -2637,7 +2637,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>15.75642871856689</v>
+        <v>15.75642776489258</v>
       </c>
       <c r="C93" t="n">
         <v>23.30999946594238</v>
@@ -2666,7 +2666,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>15.83754634857178</v>
+        <v>15.83754539489746</v>
       </c>
       <c r="C94" t="n">
         <v>23.43000030517578</v>
@@ -2695,7 +2695,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>15.36092185974121</v>
+        <v>15.36092567443848</v>
       </c>
       <c r="C95" t="n">
         <v>22.55999946594238</v>
@@ -2724,7 +2724,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>14.46895503997803</v>
+        <v>14.46895217895508</v>
       </c>
       <c r="C96" t="n">
         <v>21.25</v>
@@ -2753,7 +2753,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>15.27240562438965</v>
+        <v>15.27240467071533</v>
       </c>
       <c r="C97" t="n">
         <v>22.43000030517578</v>
@@ -2782,7 +2782,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>15.03227615356445</v>
+        <v>15.03227996826172</v>
       </c>
       <c r="C98" t="n">
         <v>21.90999984741211</v>
@@ -2811,7 +2811,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>14.95680332183838</v>
+        <v>14.95680809020996</v>
       </c>
       <c r="C99" t="n">
         <v>21.79999923706055</v>
@@ -2840,7 +2840,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>15.38217926025391</v>
+        <v>15.38218116760254</v>
       </c>
       <c r="C100" t="n">
         <v>22.42000007629395</v>
@@ -2869,7 +2869,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>15.99109935760498</v>
+        <v>15.99110889434814</v>
       </c>
       <c r="C101" t="n">
         <v>23.11000061035156</v>
@@ -2898,7 +2898,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>17.03595733642578</v>
+        <v>17.03595542907715</v>
       </c>
       <c r="C102" t="n">
         <v>24.6200008392334</v>
@@ -2927,7 +2927,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>17.19510459899902</v>
+        <v>17.19510841369629</v>
       </c>
       <c r="C103" t="n">
         <v>24.85000038146973</v>
@@ -2956,7 +2956,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>17.5913143157959</v>
+        <v>17.59132194519043</v>
       </c>
       <c r="C104" t="n">
         <v>25.22999954223633</v>
@@ -3014,7 +3014,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>17.68324089050293</v>
+        <v>17.68323135375977</v>
       </c>
       <c r="C106" t="n">
         <v>25.17000007629395</v>
@@ -3043,7 +3043,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>17.19144630432129</v>
+        <v>17.19145202636719</v>
       </c>
       <c r="C107" t="n">
         <v>24.46999931335449</v>
@@ -3072,7 +3072,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>19.41854095458984</v>
+        <v>19.41853141784668</v>
       </c>
       <c r="C108" t="n">
         <v>27.63999938964844</v>
@@ -3101,7 +3101,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>19.54499626159668</v>
+        <v>19.54499816894531</v>
       </c>
       <c r="C109" t="n">
         <v>27.81999969482422</v>
@@ -3130,7 +3130,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>18.65369606018066</v>
+        <v>18.6536922454834</v>
       </c>
       <c r="C110" t="n">
         <v>26.3700008392334</v>
@@ -3159,7 +3159,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>20.8748722076416</v>
+        <v>20.8748779296875</v>
       </c>
       <c r="C111" t="n">
         <v>29.51000022888184</v>
@@ -3188,7 +3188,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>19.6232967376709</v>
+        <v>19.62329483032227</v>
       </c>
       <c r="C112" t="n">
         <v>27.53000068664551</v>
@@ -3217,7 +3217,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>20.54992866516113</v>
+        <v>20.54993057250977</v>
       </c>
       <c r="C113" t="n">
         <v>28.82999992370605</v>
@@ -3246,7 +3246,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>20.8920783996582</v>
+        <v>20.89207077026367</v>
       </c>
       <c r="C114" t="n">
         <v>29.30999946594238</v>
@@ -3275,7 +3275,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>19.57340049743652</v>
+        <v>19.57340240478516</v>
       </c>
       <c r="C115" t="n">
         <v>27.45999908447266</v>
@@ -3304,7 +3304,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>20.41379928588867</v>
+        <v>20.4138011932373</v>
       </c>
       <c r="C116" t="n">
         <v>28.42000007629395</v>
@@ -3362,7 +3362,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>18.8551139831543</v>
+        <v>18.85511016845703</v>
       </c>
       <c r="C118" t="n">
         <v>26.25</v>
@@ -3391,7 +3391,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>20.8897819519043</v>
+        <v>20.88978576660156</v>
       </c>
       <c r="C119" t="n">
         <v>28.85000038146973</v>
@@ -3478,7 +3478,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>17.36015319824219</v>
+        <v>17.36015129089355</v>
       </c>
       <c r="C122" t="n">
         <v>23.79000091552734</v>
@@ -3507,7 +3507,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>19.10420036315918</v>
+        <v>19.10419845581055</v>
       </c>
       <c r="C123" t="n">
         <v>26.18000030517578</v>
@@ -3536,7 +3536,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>20.7752685546875</v>
+        <v>20.77526473999023</v>
       </c>
       <c r="C124" t="n">
         <v>28.46999931335449</v>
@@ -3565,7 +3565,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>20.24358749389648</v>
+        <v>20.24359321594238</v>
       </c>
       <c r="C125" t="n">
         <v>27.48999977111816</v>
@@ -3623,7 +3623,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>21.12726211547852</v>
+        <v>21.12727355957031</v>
       </c>
       <c r="C127" t="n">
         <v>28.69000053405762</v>
@@ -3652,7 +3652,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>22.68705177307129</v>
+        <v>22.68706130981445</v>
       </c>
       <c r="C128" t="n">
         <v>30.53000068664551</v>
@@ -3710,7 +3710,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>23.57135200500488</v>
+        <v>23.57135391235352</v>
       </c>
       <c r="C130" t="n">
         <v>31.71999931335449</v>
@@ -3739,7 +3739,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>22.98693656921387</v>
+        <v>22.98694038391113</v>
       </c>
       <c r="C131" t="n">
         <v>30.68000030517578</v>
@@ -3768,7 +3768,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>22.34259223937988</v>
+        <v>22.34258842468262</v>
       </c>
       <c r="C132" t="n">
         <v>29.81999969482422</v>
@@ -3797,7 +3797,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>22.64228057861328</v>
+        <v>22.64228439331055</v>
       </c>
       <c r="C133" t="n">
         <v>30.21999931335449</v>
@@ -3826,7 +3826,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>23.21454238891602</v>
+        <v>23.21454429626465</v>
       </c>
       <c r="C134" t="n">
         <v>30.71999931335449</v>
@@ -3855,7 +3855,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>25.82920265197754</v>
+        <v>25.82920074462891</v>
       </c>
       <c r="C135" t="n">
         <v>34.18000030517578</v>
@@ -3884,7 +3884,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>25.54205131530762</v>
+        <v>25.54203796386719</v>
       </c>
       <c r="C136" t="n">
         <v>33.79999923706055</v>
@@ -3942,7 +3942,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>24.03421592712402</v>
+        <v>24.03421020507812</v>
       </c>
       <c r="C138" t="n">
         <v>31.53000068664551</v>
@@ -3971,7 +3971,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>23.85889053344727</v>
+        <v>23.85888671875</v>
       </c>
       <c r="C139" t="n">
         <v>31.29999923706055</v>
@@ -4029,7 +4029,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>24.78193855285645</v>
+        <v>24.78193473815918</v>
       </c>
       <c r="C141" t="n">
         <v>32.20999908447266</v>
@@ -4058,7 +4058,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>25.87447547912598</v>
+        <v>25.87447166442871</v>
       </c>
       <c r="C142" t="n">
         <v>33.63000106811523</v>
@@ -4087,7 +4087,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>26.50160217285156</v>
+        <v>26.5015926361084</v>
       </c>
       <c r="C143" t="n">
         <v>34.15000152587891</v>
@@ -4116,7 +4116,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>28.94610595703125</v>
+        <v>28.94609832763672</v>
       </c>
       <c r="C144" t="n">
         <v>37.29999923706055</v>
@@ -4145,7 +4145,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>29.72213745117188</v>
+        <v>29.72214126586914</v>
       </c>
       <c r="C145" t="n">
         <v>38.29999923706055</v>
@@ -4174,7 +4174,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>32.47693252563477</v>
+        <v>32.47693634033203</v>
       </c>
       <c r="C146" t="n">
         <v>41.54000091552734</v>
@@ -4203,7 +4203,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>35.01004409790039</v>
+        <v>35.01003646850586</v>
       </c>
       <c r="C147" t="n">
         <v>44.77999877929688</v>
@@ -4230,7 +4230,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>33.53240585327148</v>
+        <v>33.53239822387695</v>
       </c>
       <c r="C148" t="n">
         <v>42.88999938964844</v>
@@ -4284,7 +4284,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>33.66010284423828</v>
+        <v>33.66011047363281</v>
       </c>
       <c r="C150" t="n">
         <v>42.70999908447266</v>
@@ -4338,7 +4338,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>33.58886337280273</v>
+        <v>33.58887481689453</v>
       </c>
       <c r="C152" t="n">
         <v>42.29000091552734</v>
@@ -4421,7 +4421,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>36.58265686035156</v>
+        <v>36.58264541625977</v>
       </c>
       <c r="C155" t="n">
         <v>45.75</v>
@@ -4450,7 +4450,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>38.27784729003906</v>
+        <v>38.2778434753418</v>
       </c>
       <c r="C156" t="n">
         <v>47.86999893188477</v>
@@ -4479,7 +4479,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>34.6475715637207</v>
+        <v>34.64757919311523</v>
       </c>
       <c r="C157" t="n">
         <v>43.33000183105469</v>
@@ -4537,7 +4537,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>41.71689605712891</v>
+        <v>41.71689987182617</v>
       </c>
       <c r="C159" t="n">
         <v>51.77000045776367</v>
@@ -4566,7 +4566,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>43.50579071044922</v>
+        <v>43.50579452514648</v>
       </c>
       <c r="C160" t="n">
         <v>53.9900016784668</v>
@@ -4595,7 +4595,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>45.37064361572266</v>
+        <v>45.37062835693359</v>
       </c>
       <c r="C161" t="n">
         <v>55.95000076293945</v>
@@ -4624,7 +4624,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>42.19184875488281</v>
+        <v>42.19185256958008</v>
       </c>
       <c r="C162" t="n">
         <v>52.02999877929688</v>
@@ -4682,7 +4682,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>45.20815277099609</v>
+        <v>45.20814895629883</v>
       </c>
       <c r="C164" t="n">
         <v>55.40000152587891</v>
@@ -4711,7 +4711,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>38.19844055175781</v>
+        <v>38.19844436645508</v>
       </c>
       <c r="C165" t="n">
         <v>46.81000137329102</v>
@@ -4740,7 +4740,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>40.32012557983398</v>
+        <v>40.32011795043945</v>
       </c>
       <c r="C166" t="n">
         <v>49.40999984741211</v>
@@ -4769,7 +4769,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>39.06330490112305</v>
+        <v>39.06330108642578</v>
       </c>
       <c r="C167" t="n">
         <v>47.5099983215332</v>
@@ -4798,7 +4798,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>37.25442886352539</v>
+        <v>37.25443267822266</v>
       </c>
       <c r="C168" t="n">
         <v>45.31000137329102</v>
@@ -4827,7 +4827,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>39.43329238891602</v>
+        <v>39.43331146240234</v>
       </c>
       <c r="C169" t="n">
         <v>47.95999908447266</v>
@@ -4856,7 +4856,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>38.0749626159668</v>
+        <v>38.07496643066406</v>
       </c>
       <c r="C170" t="n">
         <v>45.97000122070312</v>
@@ -4885,7 +4885,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>33.07229232788086</v>
+        <v>33.07228851318359</v>
       </c>
       <c r="C171" t="n">
         <v>39.93000030517578</v>
@@ -4943,7 +4943,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>35.43432998657227</v>
+        <v>35.434326171875</v>
       </c>
       <c r="C173" t="n">
         <v>42.38000106811523</v>
@@ -4972,7 +4972,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>39.98275756835938</v>
+        <v>39.98276519775391</v>
       </c>
       <c r="C174" t="n">
         <v>47.81999969482422</v>
@@ -5030,7 +5030,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>39.69098281860352</v>
+        <v>39.69097900390625</v>
       </c>
       <c r="C176" t="n">
         <v>47.09999847412109</v>
@@ -5059,7 +5059,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>35.57861328125</v>
+        <v>35.57862091064453</v>
       </c>
       <c r="C177" t="n">
         <v>42.22000122070312</v>
@@ -5117,7 +5117,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>30.53182411193848</v>
+        <v>30.53182601928711</v>
       </c>
       <c r="C179" t="n">
         <v>35.90000152587891</v>
@@ -5146,7 +5146,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>36.587158203125</v>
+        <v>36.58716583251953</v>
       </c>
       <c r="C180" t="n">
         <v>43.02000045776367</v>
@@ -5175,7 +5175,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>38.05847930908203</v>
+        <v>38.0584831237793</v>
       </c>
       <c r="C181" t="n">
         <v>44.75</v>
@@ -5204,7 +5204,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>38.22137451171875</v>
+        <v>38.22138214111328</v>
       </c>
       <c r="C182" t="n">
         <v>44.58000183105469</v>
@@ -5262,7 +5262,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>44.33439254760742</v>
+        <v>44.33438110351562</v>
       </c>
       <c r="C184" t="n">
         <v>51.70999908447266</v>
@@ -5291,7 +5291,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>43.96142578125</v>
+        <v>43.96142196655273</v>
       </c>
       <c r="C185" t="n">
         <v>50.90999984741211</v>
@@ -5349,7 +5349,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>45.76616668701172</v>
+        <v>45.76616287231445</v>
       </c>
       <c r="C187" t="n">
         <v>53</v>
@@ -5378,7 +5378,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>48.14604187011719</v>
+        <v>48.14603805541992</v>
       </c>
       <c r="C188" t="n">
         <v>55.36999893188477</v>
@@ -5407,7 +5407,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>51.31983947753906</v>
+        <v>51.31983184814453</v>
       </c>
       <c r="C189" t="n">
         <v>59.02000045776367</v>
@@ -5436,7 +5436,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>47.32867813110352</v>
+        <v>47.32868194580078</v>
       </c>
       <c r="C190" t="n">
         <v>54.43000030517578</v>
@@ -5465,7 +5465,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>48.99653625488281</v>
+        <v>48.99652862548828</v>
       </c>
       <c r="C191" t="n">
         <v>55.97000122070312</v>
@@ -5494,7 +5494,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>48.00732040405273</v>
+        <v>48.00732803344727</v>
       </c>
       <c r="C192" t="n">
         <v>54.84000015258789</v>
@@ -5523,7 +5523,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>55.47452926635742</v>
+        <v>55.47454071044922</v>
       </c>
       <c r="C193" t="n">
         <v>63.36999893188477</v>
@@ -5552,7 +5552,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>49.02108383178711</v>
+        <v>49.02108764648438</v>
       </c>
       <c r="C194" t="n">
         <v>55.66999816894531</v>
@@ -5610,7 +5610,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>49.10033798217773</v>
+        <v>49.10033416748047</v>
       </c>
       <c r="C196" t="n">
         <v>55.7599983215332</v>
@@ -5639,7 +5639,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>43.42546081542969</v>
+        <v>43.42545700073242</v>
       </c>
       <c r="C197" t="n">
         <v>48.97999954223633</v>
@@ -5668,7 +5668,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>39.94114303588867</v>
+        <v>39.94113540649414</v>
       </c>
       <c r="C198" t="n">
         <v>45.04999923706055</v>
@@ -5697,7 +5697,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>37.804443359375</v>
+        <v>37.80443572998047</v>
       </c>
       <c r="C199" t="n">
         <v>42.63999938964844</v>
@@ -5726,7 +5726,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>40.58689117431641</v>
+        <v>40.58689498901367</v>
       </c>
       <c r="C200" t="n">
         <v>45.36999893188477</v>
@@ -5755,7 +5755,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>40.00541305541992</v>
+        <v>40.00541687011719</v>
       </c>
       <c r="C201" t="n">
         <v>44.72000122070312</v>
@@ -5813,7 +5813,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>41.01806259155273</v>
+        <v>41.01805877685547</v>
       </c>
       <c r="C203" t="n">
         <v>45.43000030517578</v>
@@ -5842,7 +5842,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>44.89144134521484</v>
+        <v>44.89143753051758</v>
       </c>
       <c r="C204" t="n">
         <v>49.72000122070312</v>
@@ -5871,7 +5871,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>43.01344299316406</v>
+        <v>43.01343536376953</v>
       </c>
       <c r="C205" t="n">
         <v>47.63999938964844</v>
@@ -5929,7 +5929,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>44.06699371337891</v>
+        <v>44.06697845458984</v>
       </c>
       <c r="C207" t="n">
         <v>48.41999816894531</v>
@@ -5958,7 +5958,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>47.57997512817383</v>
+        <v>47.57996368408203</v>
       </c>
       <c r="C208" t="n">
         <v>52.27999877929688</v>
@@ -5987,7 +5987,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>43.32518005371094</v>
+        <v>43.32518768310547</v>
       </c>
       <c r="C209" t="n">
         <v>47.25</v>
@@ -6016,7 +6016,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>45.54416656494141</v>
+        <v>45.54417037963867</v>
       </c>
       <c r="C210" t="n">
         <v>49.66999816894531</v>
@@ -6074,7 +6074,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>48.07915115356445</v>
+        <v>48.07915496826172</v>
       </c>
       <c r="C212" t="n">
         <v>52.04000091552734</v>
@@ -6103,7 +6103,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>52.9849967956543</v>
+        <v>52.98499298095703</v>
       </c>
       <c r="C213" t="n">
         <v>57.34999847412109</v>
@@ -6132,7 +6132,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>49.66823577880859</v>
+        <v>49.66823196411133</v>
       </c>
       <c r="C214" t="n">
         <v>53.7599983215332</v>
@@ -6161,7 +6161,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>48.51013565063477</v>
+        <v>48.51013946533203</v>
       </c>
       <c r="C215" t="n">
         <v>52.13000106811523</v>
@@ -6190,7 +6190,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>45.02053070068359</v>
+        <v>45.02053833007812</v>
       </c>
       <c r="C216" t="n">
         <v>48.38000106811523</v>
@@ -6219,7 +6219,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>47.01193618774414</v>
+        <v>47.01193237304688</v>
       </c>
       <c r="C217" t="n">
         <v>50.52000045776367</v>
@@ -6248,7 +6248,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>47.05889892578125</v>
+        <v>47.05889511108398</v>
       </c>
       <c r="C218" t="n">
         <v>50.18000030517578</v>
@@ -6277,7 +6277,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>45.36146926879883</v>
+        <v>45.36147689819336</v>
       </c>
       <c r="C219" t="n">
         <v>48.36999893188477</v>
@@ -6306,7 +6306,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>46.80569076538086</v>
+        <v>46.80569458007812</v>
       </c>
       <c r="C220" t="n">
         <v>49.90999984741211</v>
@@ -6335,7 +6335,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>44.41788864135742</v>
+        <v>44.41788101196289</v>
       </c>
       <c r="C221" t="n">
         <v>46.97999954223633</v>
@@ -6364,7 +6364,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>43.96405792236328</v>
+        <v>43.96406173706055</v>
       </c>
       <c r="C222" t="n">
         <v>46.5</v>
@@ -6393,7 +6393,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>44.91897964477539</v>
+        <v>44.91897201538086</v>
       </c>
       <c r="C223" t="n">
         <v>47.5099983215332</v>
@@ -6422,7 +6422,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>46.20015716552734</v>
+        <v>46.20016098022461</v>
       </c>
       <c r="C224" t="n">
         <v>48.45000076293945</v>
@@ -6480,7 +6480,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>50.74865341186523</v>
+        <v>50.74864959716797</v>
       </c>
       <c r="C226" t="n">
         <v>53.22000122070312</v>
@@ -6538,7 +6538,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>56.89199066162109</v>
+        <v>56.89198684692383</v>
       </c>
       <c r="C228" t="n">
         <v>59.20999908447266</v>
@@ -6683,7 +6683,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>56.22078704833984</v>
+        <v>56.22077941894531</v>
       </c>
       <c r="C233" t="n">
         <v>57.72999954223633</v>
@@ -6712,7 +6712,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>61.3919677734375</v>
+        <v>61.39196395874023</v>
       </c>
       <c r="C234" t="n">
         <v>63.04000091552734</v>
@@ -6741,7 +6741,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>67.56621551513672</v>
+        <v>67.56622314453125</v>
       </c>
       <c r="C235" t="n">
         <v>69.37999725341797</v>
@@ -6857,7 +6857,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>72.05937194824219</v>
+        <v>72.05936431884766</v>
       </c>
       <c r="C239" t="n">
         <v>73.11000061035156</v>
@@ -6915,7 +6915,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>75.92303466796875</v>
+        <v>75.92304229736328</v>
       </c>
       <c r="C241" t="n">
         <v>77.02999877929688</v>
